--- a/CardData/Buff.xlsx
+++ b/CardData/Buff.xlsx
@@ -5,7 +5,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId3"/>
+    <sheet name="Buff" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0" iterate="0"/>
 </workbook>
